--- a/study/analysis/mathontospeak_synthetic_demo_analysis.xlsx
+++ b/study/analysis/mathontospeak_synthetic_demo_analysis.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1446e2dfcae24a19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stimuli" sheetId="2" r:id="R5239633a77114c1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counterbalance" sheetId="3" r:id="R66b747102eb84ef9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comprehension Scores" sheetId="4" r:id="R6111c178919f43de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NASA TLX" sheetId="5" r:id="Ra3a95f903fb84f0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCQ Items" sheetId="6" r:id="R86d0fde755a34232"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Coding" sheetId="7" r:id="R8f43ef93ea214080"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo Provenance" sheetId="8" r:id="R21351249e65646f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R26c565d4f3324d80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stimuli" sheetId="2" r:id="Rdc4dd7dbfad04717"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counterbalance" sheetId="3" r:id="Re9e75771b1984074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comprehension Scores" sheetId="4" r:id="R81de29042b6846c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NASA TLX" sheetId="5" r:id="Refa57c2005604abc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCQ Items" sheetId="6" r:id="R5300ce425b8a4a81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Coding" sheetId="7" r:id="R0a3abe2d5a2c4fe3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo Provenance" sheetId="8" r:id="R566f88930fea424f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1124,17 +1124,17 @@
         <x:v>ALG01_Q2</x:v>
       </x:c>
       <x:c r="E6" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F6" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G6" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H6" s="14" t="n">
         <x:f>IF(G6="Yes",1,IF(G6="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1178,17 +1178,17 @@
         <x:v>ALG01_Q4</x:v>
       </x:c>
       <x:c r="E8" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F8" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G8" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H8" s="14" t="n">
         <x:f>IF(G8="Yes",1,IF(G8="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1205,17 +1205,17 @@
         <x:v>ALG02_Q1</x:v>
       </x:c>
       <x:c r="E9" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G9" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H9" s="14" t="n">
         <x:f>IF(G9="Yes",1,IF(G9="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1232,17 +1232,17 @@
         <x:v>ALG02_Q2</x:v>
       </x:c>
       <x:c r="E10" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G10" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H10" s="14" t="n">
         <x:f>IF(G10="Yes",1,IF(G10="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1313,17 +1313,17 @@
         <x:v>ALG03_Q1</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F13" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G13" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="14" t="n">
         <x:f>IF(G13="Yes",1,IF(G13="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1475,17 +1475,17 @@
         <x:v>ALG04_Q3</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F19" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G19" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="14" t="n">
         <x:f>IF(G19="Yes",1,IF(G19="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1556,17 +1556,17 @@
         <x:v>CALC01_Q2</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F22" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G22" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H22" s="14" t="n">
         <x:f>IF(G22="Yes",1,IF(G22="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1610,17 +1610,17 @@
         <x:v>CALC01_Q4</x:v>
       </x:c>
       <x:c r="E24" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F24" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G24" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="14" t="n">
         <x:f>IF(G24="Yes",1,IF(G24="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1637,17 +1637,17 @@
         <x:v>CALC02_Q1</x:v>
       </x:c>
       <x:c r="E25" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F25" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G25" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H25" s="14" t="n">
         <x:f>IF(G25="Yes",1,IF(G25="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1664,17 +1664,17 @@
         <x:v>CALC02_Q2</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F26" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G26" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H26" s="14" t="n">
         <x:f>IF(G26="Yes",1,IF(G26="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1745,17 +1745,17 @@
         <x:v>CALC03_Q1</x:v>
       </x:c>
       <x:c r="E29" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F29" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G29" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H29" s="14" t="n">
         <x:f>IF(G29="Yes",1,IF(G29="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1907,17 +1907,17 @@
         <x:v>LIN01_Q3</x:v>
       </x:c>
       <x:c r="E35" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F35" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G35" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H35" s="14" t="n">
         <x:f>IF(G35="Yes",1,IF(G35="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1988,17 +1988,17 @@
         <x:v>LIN02_Q2</x:v>
       </x:c>
       <x:c r="E38" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F38" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G38" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H38" s="14" t="n">
         <x:f>IF(G38="Yes",1,IF(G38="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2042,17 +2042,17 @@
         <x:v>LIN02_Q4</x:v>
       </x:c>
       <x:c r="E40" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F40" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G40" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H40" s="14" t="n">
         <x:f>IF(G40="Yes",1,IF(G40="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2069,17 +2069,17 @@
         <x:v>LIN03_Q1</x:v>
       </x:c>
       <x:c r="E41" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F41" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G41" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H41" s="14" t="n">
         <x:f>IF(G41="Yes",1,IF(G41="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -2096,17 +2096,17 @@
         <x:v>LIN03_Q2</x:v>
       </x:c>
       <x:c r="E42" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F42" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G42" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H42" s="14" t="n">
         <x:f>IF(G42="Yes",1,IF(G42="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2231,17 +2231,17 @@
         <x:v>ALG01_Q3</x:v>
       </x:c>
       <x:c r="E47" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F47" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G47" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H47" s="14" t="n">
         <x:f>IF(G47="Yes",1,IF(G47="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -2312,17 +2312,17 @@
         <x:v>ALG02_Q2</x:v>
       </x:c>
       <x:c r="E50" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F50" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G50" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H50" s="14" t="n">
         <x:f>IF(G50="Yes",1,IF(G50="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -2393,17 +2393,17 @@
         <x:v>ALG03_Q1</x:v>
       </x:c>
       <x:c r="E53" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F53" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G53" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H53" s="14" t="n">
         <x:f>IF(G53="Yes",1,IF(G53="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -2501,17 +2501,17 @@
         <x:v>ALG04_Q1</x:v>
       </x:c>
       <x:c r="E57" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F57" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G57" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H57" s="14" t="n">
         <x:f>IF(G57="Yes",1,IF(G57="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -2528,17 +2528,17 @@
         <x:v>ALG04_Q2</x:v>
       </x:c>
       <x:c r="E58" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F58" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G58" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H58" s="14" t="n">
         <x:f>IF(G58="Yes",1,IF(G58="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -2663,17 +2663,17 @@
         <x:v>CALC01_Q3</x:v>
       </x:c>
       <x:c r="E63" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F63" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G63" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H63" s="14" t="n">
         <x:f>IF(G63="Yes",1,IF(G63="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -2690,17 +2690,17 @@
         <x:v>CALC01_Q4</x:v>
       </x:c>
       <x:c r="E64" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F64" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G64" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H64" s="14" t="n">
         <x:f>IF(G64="Yes",1,IF(G64="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -2879,17 +2879,17 @@
         <x:v>CALC03_Q3</x:v>
       </x:c>
       <x:c r="E71" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F71" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G71" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H71" s="14" t="n">
         <x:f>IF(G71="Yes",1,IF(G71="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -2960,17 +2960,17 @@
         <x:v>LIN01_Q2</x:v>
       </x:c>
       <x:c r="E74" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F74" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G74" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H74" s="14" t="n">
         <x:f>IF(G74="Yes",1,IF(G74="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -3068,17 +3068,17 @@
         <x:v>LIN02_Q2</x:v>
       </x:c>
       <x:c r="E78" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F78" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G78" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H78" s="14" t="n">
         <x:f>IF(G78="Yes",1,IF(G78="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -3095,17 +3095,17 @@
         <x:v>LIN02_Q3</x:v>
       </x:c>
       <x:c r="E79" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F79" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G79" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H79" s="14" t="n">
         <x:f>IF(G79="Yes",1,IF(G79="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -3230,17 +3230,17 @@
         <x:v>LIN03_Q4</x:v>
       </x:c>
       <x:c r="E84" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F84" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G84" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H84" s="14" t="n">
         <x:f>IF(G84="Yes",1,IF(G84="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -3257,17 +3257,17 @@
         <x:v>ALG01_Q1</x:v>
       </x:c>
       <x:c r="E85" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F85" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G85" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H85" s="14" t="n">
         <x:f>IF(G85="Yes",1,IF(G85="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -3365,17 +3365,17 @@
         <x:v>ALG02_Q1</x:v>
       </x:c>
       <x:c r="E89" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F89" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G89" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H89" s="14" t="n">
         <x:f>IF(G89="Yes",1,IF(G89="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -3419,17 +3419,17 @@
         <x:v>ALG02_Q3</x:v>
       </x:c>
       <x:c r="E91" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F91" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G91" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H91" s="14" t="n">
         <x:f>IF(G91="Yes",1,IF(G91="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -3689,17 +3689,17 @@
         <x:v>CALC01_Q1</x:v>
       </x:c>
       <x:c r="E101" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F101" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G101" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H101" s="14" t="n">
         <x:f>IF(G101="Yes",1,IF(G101="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -3743,17 +3743,17 @@
         <x:v>CALC01_Q3</x:v>
       </x:c>
       <x:c r="E103" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F103" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G103" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H103" s="14" t="n">
         <x:f>IF(G103="Yes",1,IF(G103="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -3932,17 +3932,17 @@
         <x:v>CALC03_Q2</x:v>
       </x:c>
       <x:c r="E110" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F110" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G110" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H110" s="14" t="n">
         <x:f>IF(G110="Yes",1,IF(G110="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -3986,17 +3986,17 @@
         <x:v>CALC03_Q4</x:v>
       </x:c>
       <x:c r="E112" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F112" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G112" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H112" s="14" t="n">
         <x:f>IF(G112="Yes",1,IF(G112="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -4310,17 +4310,17 @@
         <x:v>LIN03_Q4</x:v>
       </x:c>
       <x:c r="E124" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F124" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G124" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H124" s="14" t="n">
         <x:f>IF(G124="Yes",1,IF(G124="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -4364,17 +4364,17 @@
         <x:v>ALG01_Q2</x:v>
       </x:c>
       <x:c r="E126" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F126" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G126" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H126" s="14" t="n">
         <x:f>IF(G126="Yes",1,IF(G126="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -4418,17 +4418,17 @@
         <x:v>ALG01_Q4</x:v>
       </x:c>
       <x:c r="E128" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F128" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G128" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H128" s="14" t="n">
         <x:f>IF(G128="Yes",1,IF(G128="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -4499,17 +4499,17 @@
         <x:v>ALG02_Q3</x:v>
       </x:c>
       <x:c r="E131" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F131" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G131" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H131" s="14" t="n">
         <x:f>IF(G131="Yes",1,IF(G131="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -4634,17 +4634,17 @@
         <x:v>ALG03_Q4</x:v>
       </x:c>
       <x:c r="E136" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F136" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G136" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H136" s="14" t="n">
         <x:f>IF(G136="Yes",1,IF(G136="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -4661,17 +4661,17 @@
         <x:v>ALG04_Q1</x:v>
       </x:c>
       <x:c r="E137" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F137" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G137" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H137" s="14" t="n">
         <x:f>IF(G137="Yes",1,IF(G137="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -4742,17 +4742,17 @@
         <x:v>ALG04_Q4</x:v>
       </x:c>
       <x:c r="E140" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F140" s="13" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G140" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H140" s="14" t="n">
         <x:f>IF(G140="Yes",1,IF(G140="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -4796,17 +4796,17 @@
         <x:v>CALC01_Q2</x:v>
       </x:c>
       <x:c r="E142" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F142" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G142" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H142" s="14" t="n">
         <x:f>IF(G142="Yes",1,IF(G142="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -4850,17 +4850,17 @@
         <x:v>CALC01_Q4</x:v>
       </x:c>
       <x:c r="E144" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F144" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G144" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H144" s="14" t="n">
         <x:f>IF(G144="Yes",1,IF(G144="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -4931,17 +4931,17 @@
         <x:v>CALC02_Q3</x:v>
       </x:c>
       <x:c r="E147" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F147" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G147" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H147" s="14" t="n">
         <x:f>IF(G147="Yes",1,IF(G147="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -5093,17 +5093,17 @@
         <x:v>LIN01_Q1</x:v>
       </x:c>
       <x:c r="E153" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F153" s="13" t="str">
         <x:v>Functions</x:v>
       </x:c>
       <x:c r="G153" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H153" s="14" t="n">
         <x:f>IF(G153="Yes",1,IF(G153="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -5174,17 +5174,17 @@
         <x:v>LIN01_Q4</x:v>
       </x:c>
       <x:c r="E156" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F156" s="13" t="str">
         <x:v>6)</x:v>
       </x:c>
       <x:c r="G156" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H156" s="14" t="n">
         <x:f>IF(G156="Yes",1,IF(G156="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -5228,17 +5228,17 @@
         <x:v>LIN02_Q2</x:v>
       </x:c>
       <x:c r="E158" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F158" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G158" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H158" s="14" t="n">
         <x:f>IF(G158="Yes",1,IF(G158="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -5282,17 +5282,17 @@
         <x:v>LIN02_Q4</x:v>
       </x:c>
       <x:c r="E160" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F160" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G160" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H160" s="14" t="n">
         <x:f>IF(G160="Yes",1,IF(G160="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -5363,17 +5363,17 @@
         <x:v>LIN03_Q3</x:v>
       </x:c>
       <x:c r="E163" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F163" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G163" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H163" s="14" t="n">
         <x:f>IF(G163="Yes",1,IF(G163="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -5444,17 +5444,17 @@
         <x:v>ALG01_Q2</x:v>
       </x:c>
       <x:c r="E166" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F166" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G166" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H166" s="14" t="n">
         <x:f>IF(G166="Yes",1,IF(G166="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -5525,17 +5525,17 @@
         <x:v>ALG02_Q1</x:v>
       </x:c>
       <x:c r="E169" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F169" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G169" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H169" s="14" t="n">
         <x:f>IF(G169="Yes",1,IF(G169="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -5660,17 +5660,17 @@
         <x:v>ALG03_Q2</x:v>
       </x:c>
       <x:c r="E174" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F174" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G174" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H174" s="14" t="n">
         <x:f>IF(G174="Yes",1,IF(G174="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -5687,17 +5687,17 @@
         <x:v>ALG03_Q3</x:v>
       </x:c>
       <x:c r="E175" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F175" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G175" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H175" s="14" t="n">
         <x:f>IF(G175="Yes",1,IF(G175="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -5768,17 +5768,17 @@
         <x:v>ALG04_Q2</x:v>
       </x:c>
       <x:c r="E178" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F178" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G178" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H178" s="14" t="n">
         <x:f>IF(G178="Yes",1,IF(G178="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -5822,17 +5822,17 @@
         <x:v>ALG04_Q4</x:v>
       </x:c>
       <x:c r="E180" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F180" s="13" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G180" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H180" s="14" t="n">
         <x:f>IF(G180="Yes",1,IF(G180="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -5876,17 +5876,17 @@
         <x:v>CALC01_Q2</x:v>
       </x:c>
       <x:c r="E182" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F182" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G182" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H182" s="14" t="n">
         <x:f>IF(G182="Yes",1,IF(G182="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -5957,17 +5957,17 @@
         <x:v>CALC02_Q1</x:v>
       </x:c>
       <x:c r="E185" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F185" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G185" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H185" s="14" t="n">
         <x:f>IF(G185="Yes",1,IF(G185="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -6092,17 +6092,17 @@
         <x:v>CALC03_Q2</x:v>
       </x:c>
       <x:c r="E190" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F190" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G190" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H190" s="14" t="n">
         <x:f>IF(G190="Yes",1,IF(G190="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -6119,17 +6119,17 @@
         <x:v>CALC03_Q3</x:v>
       </x:c>
       <x:c r="E191" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F191" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G191" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H191" s="14" t="n">
         <x:f>IF(G191="Yes",1,IF(G191="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -6200,17 +6200,17 @@
         <x:v>LIN01_Q2</x:v>
       </x:c>
       <x:c r="E194" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F194" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G194" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H194" s="14" t="n">
         <x:f>IF(G194="Yes",1,IF(G194="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -6254,17 +6254,17 @@
         <x:v>LIN01_Q4</x:v>
       </x:c>
       <x:c r="E196" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F196" s="13" t="str">
         <x:v>6)</x:v>
       </x:c>
       <x:c r="G196" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H196" s="14" t="n">
         <x:f>IF(G196="Yes",1,IF(G196="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -6308,17 +6308,17 @@
         <x:v>LIN02_Q2</x:v>
       </x:c>
       <x:c r="E198" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F198" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G198" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H198" s="14" t="n">
         <x:f>IF(G198="Yes",1,IF(G198="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -6389,17 +6389,17 @@
         <x:v>LIN03_Q1</x:v>
       </x:c>
       <x:c r="E201" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F201" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G201" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H201" s="14" t="n">
         <x:f>IF(G201="Yes",1,IF(G201="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -6578,17 +6578,17 @@
         <x:v>ALG01_Q4</x:v>
       </x:c>
       <x:c r="E208" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F208" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G208" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H208" s="14" t="n">
         <x:f>IF(G208="Yes",1,IF(G208="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -6605,17 +6605,17 @@
         <x:v>ALG02_Q1</x:v>
       </x:c>
       <x:c r="E209" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F209" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G209" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H209" s="14" t="n">
         <x:f>IF(G209="Yes",1,IF(G209="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -6740,17 +6740,17 @@
         <x:v>ALG03_Q2</x:v>
       </x:c>
       <x:c r="E214" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F214" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G214" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H214" s="14" t="n">
         <x:f>IF(G214="Yes",1,IF(G214="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -6767,17 +6767,17 @@
         <x:v>ALG03_Q3</x:v>
       </x:c>
       <x:c r="E215" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F215" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G215" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H215" s="14" t="n">
         <x:f>IF(G215="Yes",1,IF(G215="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -6875,17 +6875,17 @@
         <x:v>ALG04_Q3</x:v>
       </x:c>
       <x:c r="E219" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F219" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G219" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H219" s="14" t="n">
         <x:f>IF(G219="Yes",1,IF(G219="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -6956,17 +6956,17 @@
         <x:v>CALC01_Q2</x:v>
       </x:c>
       <x:c r="E222" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F222" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G222" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H222" s="14" t="n">
         <x:f>IF(G222="Yes",1,IF(G222="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
@@ -7145,17 +7145,17 @@
         <x:v>CALC03_Q1</x:v>
       </x:c>
       <x:c r="E229" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F229" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G229" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H229" s="14" t="n">
         <x:f>IF(G229="Yes",1,IF(G229="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -7172,17 +7172,17 @@
         <x:v>CALC03_Q2</x:v>
       </x:c>
       <x:c r="E230" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F230" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G230" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H230" s="14" t="n">
         <x:f>IF(G230="Yes",1,IF(G230="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -7307,17 +7307,17 @@
         <x:v>LIN01_Q3</x:v>
       </x:c>
       <x:c r="E235" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F235" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G235" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H235" s="14" t="n">
         <x:f>IF(G235="Yes",1,IF(G235="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
@@ -7334,17 +7334,17 @@
         <x:v>LIN01_Q4</x:v>
       </x:c>
       <x:c r="E236" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F236" s="13" t="str">
         <x:v>6)</x:v>
       </x:c>
       <x:c r="G236" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H236" s="14" t="n">
         <x:f>IF(G236="Yes",1,IF(G236="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -7523,17 +7523,17 @@
         <x:v>LIN03_Q3</x:v>
       </x:c>
       <x:c r="E243" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F243" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G243" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H243" s="14" t="n">
         <x:f>IF(G243="Yes",1,IF(G243="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
@@ -7766,17 +7766,17 @@
         <x:v>ALG02_Q4</x:v>
       </x:c>
       <x:c r="E252" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F252" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G252" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H252" s="14" t="n">
         <x:f>IF(G252="Yes",1,IF(G252="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="253">
@@ -7820,17 +7820,17 @@
         <x:v>ALG03_Q2</x:v>
       </x:c>
       <x:c r="E254" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F254" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G254" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H254" s="14" t="n">
         <x:f>IF(G254="Yes",1,IF(G254="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="255">
@@ -7901,17 +7901,17 @@
         <x:v>ALG04_Q1</x:v>
       </x:c>
       <x:c r="E257" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F257" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G257" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H257" s="14" t="n">
         <x:f>IF(G257="Yes",1,IF(G257="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -7928,17 +7928,17 @@
         <x:v>ALG04_Q2</x:v>
       </x:c>
       <x:c r="E258" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F258" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G258" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H258" s="14" t="n">
         <x:f>IF(G258="Yes",1,IF(G258="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -8009,17 +8009,17 @@
         <x:v>CALC01_Q1</x:v>
       </x:c>
       <x:c r="E261" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F261" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G261" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H261" s="14" t="n">
         <x:f>IF(G261="Yes",1,IF(G261="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="262">
@@ -8063,17 +8063,17 @@
         <x:v>CALC01_Q3</x:v>
       </x:c>
       <x:c r="E263" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F263" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G263" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H263" s="14" t="n">
         <x:f>IF(G263="Yes",1,IF(G263="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
@@ -8333,17 +8333,17 @@
         <x:v>LIN01_Q1</x:v>
       </x:c>
       <x:c r="E273" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F273" s="13" t="str">
         <x:v>Functions</x:v>
       </x:c>
       <x:c r="G273" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H273" s="14" t="n">
         <x:f>IF(G273="Yes",1,IF(G273="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
@@ -8387,17 +8387,17 @@
         <x:v>LIN01_Q3</x:v>
       </x:c>
       <x:c r="E275" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F275" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G275" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H275" s="14" t="n">
         <x:f>IF(G275="Yes",1,IF(G275="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
@@ -8495,17 +8495,17 @@
         <x:v>LIN02_Q3</x:v>
       </x:c>
       <x:c r="E279" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F279" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G279" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H279" s="14" t="n">
         <x:f>IF(G279="Yes",1,IF(G279="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -8576,17 +8576,17 @@
         <x:v>LIN03_Q2</x:v>
       </x:c>
       <x:c r="E282" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F282" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G282" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H282" s="14" t="n">
         <x:f>IF(G282="Yes",1,IF(G282="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="283">
@@ -8630,17 +8630,17 @@
         <x:v>LIN03_Q4</x:v>
       </x:c>
       <x:c r="E284" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F284" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G284" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H284" s="14" t="n">
         <x:f>IF(G284="Yes",1,IF(G284="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
@@ -8711,17 +8711,17 @@
         <x:v>ALG01_Q3</x:v>
       </x:c>
       <x:c r="E287" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F287" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G287" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H287" s="14" t="n">
         <x:f>IF(G287="Yes",1,IF(G287="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -8846,17 +8846,17 @@
         <x:v>ALG02_Q4</x:v>
       </x:c>
       <x:c r="E292" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F292" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G292" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H292" s="14" t="n">
         <x:f>IF(G292="Yes",1,IF(G292="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="293">
@@ -8873,17 +8873,17 @@
         <x:v>ALG03_Q1</x:v>
       </x:c>
       <x:c r="E293" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F293" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G293" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H293" s="14" t="n">
         <x:f>IF(G293="Yes",1,IF(G293="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -8954,17 +8954,17 @@
         <x:v>ALG03_Q4</x:v>
       </x:c>
       <x:c r="E296" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F296" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G296" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H296" s="14" t="n">
         <x:f>IF(G296="Yes",1,IF(G296="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="297">
@@ -9008,17 +9008,17 @@
         <x:v>ALG04_Q2</x:v>
       </x:c>
       <x:c r="E298" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F298" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G298" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H298" s="14" t="n">
         <x:f>IF(G298="Yes",1,IF(G298="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="299">
@@ -9062,17 +9062,17 @@
         <x:v>ALG04_Q4</x:v>
       </x:c>
       <x:c r="E300" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F300" s="13" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G300" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H300" s="14" t="n">
         <x:f>IF(G300="Yes",1,IF(G300="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="301">
@@ -9143,17 +9143,17 @@
         <x:v>CALC01_Q3</x:v>
       </x:c>
       <x:c r="E303" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F303" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G303" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H303" s="14" t="n">
         <x:f>IF(G303="Yes",1,IF(G303="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="304">
@@ -9278,17 +9278,17 @@
         <x:v>CALC02_Q4</x:v>
       </x:c>
       <x:c r="E308" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F308" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G308" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H308" s="14" t="n">
         <x:f>IF(G308="Yes",1,IF(G308="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="309">
@@ -9305,17 +9305,17 @@
         <x:v>CALC03_Q1</x:v>
       </x:c>
       <x:c r="E309" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F309" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G309" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H309" s="14" t="n">
         <x:f>IF(G309="Yes",1,IF(G309="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="310">
@@ -9386,17 +9386,17 @@
         <x:v>CALC03_Q4</x:v>
       </x:c>
       <x:c r="E312" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F312" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G312" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H312" s="14" t="n">
         <x:f>IF(G312="Yes",1,IF(G312="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="313">
@@ -9440,17 +9440,17 @@
         <x:v>LIN01_Q2</x:v>
       </x:c>
       <x:c r="E314" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F314" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G314" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H314" s="14" t="n">
         <x:f>IF(G314="Yes",1,IF(G314="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
@@ -9494,17 +9494,17 @@
         <x:v>LIN01_Q4</x:v>
       </x:c>
       <x:c r="E316" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F316" s="13" t="str">
         <x:v>6)</x:v>
       </x:c>
       <x:c r="G316" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H316" s="14" t="n">
         <x:f>IF(G316="Yes",1,IF(G316="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="317">
@@ -9575,17 +9575,17 @@
         <x:v>LIN02_Q3</x:v>
       </x:c>
       <x:c r="E319" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F319" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G319" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H319" s="14" t="n">
         <x:f>IF(G319="Yes",1,IF(G319="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
@@ -9602,17 +9602,17 @@
         <x:v>LIN02_Q4</x:v>
       </x:c>
       <x:c r="E320" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F320" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G320" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H320" s="14" t="n">
         <x:f>IF(G320="Yes",1,IF(G320="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="321">
@@ -9710,17 +9710,17 @@
         <x:v>LIN03_Q4</x:v>
       </x:c>
       <x:c r="E324" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F324" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G324" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H324" s="14" t="n">
         <x:f>IF(G324="Yes",1,IF(G324="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="325">
@@ -9737,17 +9737,17 @@
         <x:v>ALG01_Q1</x:v>
       </x:c>
       <x:c r="E325" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F325" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G325" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H325" s="14" t="n">
         <x:f>IF(G325="Yes",1,IF(G325="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="326">
@@ -9872,17 +9872,17 @@
         <x:v>ALG02_Q2</x:v>
       </x:c>
       <x:c r="E330" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F330" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G330" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H330" s="14" t="n">
         <x:f>IF(G330="Yes",1,IF(G330="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="331">
@@ -9899,17 +9899,17 @@
         <x:v>ALG02_Q3</x:v>
       </x:c>
       <x:c r="E331" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F331" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G331" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H331" s="14" t="n">
         <x:f>IF(G331="Yes",1,IF(G331="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="332">
@@ -9980,17 +9980,17 @@
         <x:v>ALG03_Q2</x:v>
       </x:c>
       <x:c r="E334" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F334" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G334" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H334" s="14" t="n">
         <x:f>IF(G334="Yes",1,IF(G334="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="335">
@@ -10034,17 +10034,17 @@
         <x:v>ALG03_Q4</x:v>
       </x:c>
       <x:c r="E336" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F336" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G336" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H336" s="14" t="n">
         <x:f>IF(G336="Yes",1,IF(G336="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="337">
@@ -10088,17 +10088,17 @@
         <x:v>ALG04_Q2</x:v>
       </x:c>
       <x:c r="E338" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F338" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G338" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H338" s="14" t="n">
         <x:f>IF(G338="Yes",1,IF(G338="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="339">
@@ -10169,17 +10169,17 @@
         <x:v>CALC01_Q1</x:v>
       </x:c>
       <x:c r="E341" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F341" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G341" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H341" s="14" t="n">
         <x:f>IF(G341="Yes",1,IF(G341="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="342">
@@ -10304,17 +10304,17 @@
         <x:v>CALC02_Q2</x:v>
       </x:c>
       <x:c r="E346" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F346" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G346" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H346" s="14" t="n">
         <x:f>IF(G346="Yes",1,IF(G346="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="347">
@@ -10331,17 +10331,17 @@
         <x:v>CALC02_Q3</x:v>
       </x:c>
       <x:c r="E347" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F347" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G347" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H347" s="14" t="n">
         <x:f>IF(G347="Yes",1,IF(G347="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="348">
@@ -10412,17 +10412,17 @@
         <x:v>CALC03_Q2</x:v>
       </x:c>
       <x:c r="E350" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F350" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G350" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H350" s="14" t="n">
         <x:f>IF(G350="Yes",1,IF(G350="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="351">
@@ -10466,17 +10466,17 @@
         <x:v>CALC03_Q4</x:v>
       </x:c>
       <x:c r="E352" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F352" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G352" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H352" s="14" t="n">
         <x:f>IF(G352="Yes",1,IF(G352="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="353">
@@ -10520,17 +10520,17 @@
         <x:v>LIN01_Q2</x:v>
       </x:c>
       <x:c r="E354" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F354" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G354" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H354" s="14" t="n">
         <x:f>IF(G354="Yes",1,IF(G354="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="355">
@@ -10601,17 +10601,17 @@
         <x:v>LIN02_Q1</x:v>
       </x:c>
       <x:c r="E357" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F357" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G357" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H357" s="14" t="n">
         <x:f>IF(G357="Yes",1,IF(G357="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="358">
@@ -10736,17 +10736,17 @@
         <x:v>LIN03_Q2</x:v>
       </x:c>
       <x:c r="E362" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F362" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G362" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H362" s="14" t="n">
         <x:f>IF(G362="Yes",1,IF(G362="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="363">
@@ -10763,17 +10763,17 @@
         <x:v>LIN03_Q3</x:v>
       </x:c>
       <x:c r="E363" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F363" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G363" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H363" s="14" t="n">
         <x:f>IF(G363="Yes",1,IF(G363="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="364">
@@ -10844,17 +10844,17 @@
         <x:v>ALG01_Q2</x:v>
       </x:c>
       <x:c r="E366" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F366" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G366" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H366" s="14" t="n">
         <x:f>IF(G366="Yes",1,IF(G366="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="367">
@@ -10952,17 +10952,17 @@
         <x:v>ALG02_Q2</x:v>
       </x:c>
       <x:c r="E370" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F370" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G370" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H370" s="14" t="n">
         <x:f>IF(G370="Yes",1,IF(G370="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="371">
@@ -11033,17 +11033,17 @@
         <x:v>ALG03_Q1</x:v>
       </x:c>
       <x:c r="E373" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F373" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G373" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H373" s="14" t="n">
         <x:f>IF(G373="Yes",1,IF(G373="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="374">
@@ -11087,17 +11087,17 @@
         <x:v>ALG03_Q3</x:v>
       </x:c>
       <x:c r="E375" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F375" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G375" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H375" s="14" t="n">
         <x:f>IF(G375="Yes",1,IF(G375="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="376">
@@ -11222,17 +11222,17 @@
         <x:v>ALG04_Q4</x:v>
       </x:c>
       <x:c r="E380" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F380" s="13" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G380" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H380" s="14" t="n">
         <x:f>IF(G380="Yes",1,IF(G380="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="381">
@@ -11384,17 +11384,17 @@
         <x:v>CALC02_Q2</x:v>
       </x:c>
       <x:c r="E386" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F386" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G386" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H386" s="14" t="n">
         <x:f>IF(G386="Yes",1,IF(G386="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="387">
@@ -11411,17 +11411,17 @@
         <x:v>CALC02_Q3</x:v>
       </x:c>
       <x:c r="E387" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F387" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G387" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H387" s="14" t="n">
         <x:f>IF(G387="Yes",1,IF(G387="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="388">
@@ -11519,17 +11519,17 @@
         <x:v>CALC03_Q3</x:v>
       </x:c>
       <x:c r="E391" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F391" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G391" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H391" s="14" t="n">
         <x:f>IF(G391="Yes",1,IF(G391="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="392">
@@ -11600,17 +11600,17 @@
         <x:v>LIN01_Q2</x:v>
       </x:c>
       <x:c r="E394" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F394" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G394" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H394" s="14" t="n">
         <x:f>IF(G394="Yes",1,IF(G394="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="395">
@@ -11789,17 +11789,17 @@
         <x:v>LIN03_Q1</x:v>
       </x:c>
       <x:c r="E401" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F401" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G401" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H401" s="14" t="n">
         <x:f>IF(G401="Yes",1,IF(G401="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="402">
@@ -11897,17 +11897,17 @@
         <x:v>ALG01_Q1</x:v>
       </x:c>
       <x:c r="E405" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F405" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G405" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H405" s="14" t="n">
         <x:f>IF(G405="Yes",1,IF(G405="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="406">
@@ -11978,17 +11978,17 @@
         <x:v>ALG01_Q4</x:v>
       </x:c>
       <x:c r="E408" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F408" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G408" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H408" s="14" t="n">
         <x:f>IF(G408="Yes",1,IF(G408="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="409">
@@ -12086,17 +12086,17 @@
         <x:v>ALG02_Q4</x:v>
       </x:c>
       <x:c r="E412" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F412" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G412" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H412" s="14" t="n">
         <x:f>IF(G412="Yes",1,IF(G412="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="413">
@@ -12113,17 +12113,17 @@
         <x:v>ALG03_Q1</x:v>
       </x:c>
       <x:c r="E413" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F413" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G413" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H413" s="14" t="n">
         <x:f>IF(G413="Yes",1,IF(G413="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="414">
@@ -12140,17 +12140,17 @@
         <x:v>ALG03_Q2</x:v>
       </x:c>
       <x:c r="E414" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F414" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G414" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H414" s="14" t="n">
         <x:f>IF(G414="Yes",1,IF(G414="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="415">
@@ -12410,17 +12410,17 @@
         <x:v>CALC01_Q4</x:v>
       </x:c>
       <x:c r="E424" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F424" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G424" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H424" s="14" t="n">
         <x:f>IF(G424="Yes",1,IF(G424="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="425">
@@ -12464,17 +12464,17 @@
         <x:v>CALC02_Q2</x:v>
       </x:c>
       <x:c r="E426" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F426" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G426" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H426" s="14" t="n">
         <x:f>IF(G426="Yes",1,IF(G426="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="427">
@@ -12545,17 +12545,17 @@
         <x:v>CALC03_Q1</x:v>
       </x:c>
       <x:c r="E429" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F429" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G429" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H429" s="14" t="n">
         <x:f>IF(G429="Yes",1,IF(G429="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="430">
@@ -12653,17 +12653,17 @@
         <x:v>LIN01_Q1</x:v>
       </x:c>
       <x:c r="E433" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F433" s="13" t="str">
         <x:v>Functions</x:v>
       </x:c>
       <x:c r="G433" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H433" s="14" t="n">
         <x:f>IF(G433="Yes",1,IF(G433="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="434">
@@ -12707,17 +12707,17 @@
         <x:v>LIN01_Q3</x:v>
       </x:c>
       <x:c r="E435" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F435" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G435" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H435" s="14" t="n">
         <x:f>IF(G435="Yes",1,IF(G435="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="436">
@@ -13058,17 +13058,17 @@
         <x:v>ALG01_Q4</x:v>
       </x:c>
       <x:c r="E448" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F448" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G448" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H448" s="14" t="n">
         <x:f>IF(G448="Yes",1,IF(G448="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="449">
@@ -13085,17 +13085,17 @@
         <x:v>ALG02_Q1</x:v>
       </x:c>
       <x:c r="E449" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F449" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G449" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H449" s="14" t="n">
         <x:f>IF(G449="Yes",1,IF(G449="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="450">
@@ -13112,17 +13112,17 @@
         <x:v>ALG02_Q2</x:v>
       </x:c>
       <x:c r="E450" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F450" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G450" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H450" s="14" t="n">
         <x:f>IF(G450="Yes",1,IF(G450="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="451">
@@ -13166,17 +13166,17 @@
         <x:v>ALG02_Q4</x:v>
       </x:c>
       <x:c r="E452" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F452" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G452" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H452" s="14" t="n">
         <x:f>IF(G452="Yes",1,IF(G452="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="453">
@@ -13220,17 +13220,17 @@
         <x:v>ALG03_Q2</x:v>
       </x:c>
       <x:c r="E454" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F454" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G454" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H454" s="14" t="n">
         <x:f>IF(G454="Yes",1,IF(G454="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="455">
@@ -13247,17 +13247,17 @@
         <x:v>ALG03_Q3</x:v>
       </x:c>
       <x:c r="E455" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F455" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G455" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H455" s="14" t="n">
         <x:f>IF(G455="Yes",1,IF(G455="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="456">
@@ -13274,17 +13274,17 @@
         <x:v>ALG03_Q4</x:v>
       </x:c>
       <x:c r="E456" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F456" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G456" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H456" s="14" t="n">
         <x:f>IF(G456="Yes",1,IF(G456="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
@@ -13355,17 +13355,17 @@
         <x:v>ALG04_Q3</x:v>
       </x:c>
       <x:c r="E459" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F459" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G459" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H459" s="14" t="n">
         <x:f>IF(G459="Yes",1,IF(G459="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="460">
@@ -13490,17 +13490,17 @@
         <x:v>CALC01_Q4</x:v>
       </x:c>
       <x:c r="E464" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F464" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G464" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H464" s="14" t="n">
         <x:f>IF(G464="Yes",1,IF(G464="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="465">
@@ -13517,17 +13517,17 @@
         <x:v>CALC02_Q1</x:v>
       </x:c>
       <x:c r="E465" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F465" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G465" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H465" s="14" t="n">
         <x:f>IF(G465="Yes",1,IF(G465="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="466">
@@ -13544,17 +13544,17 @@
         <x:v>CALC02_Q2</x:v>
       </x:c>
       <x:c r="E466" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F466" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G466" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H466" s="14" t="n">
         <x:f>IF(G466="Yes",1,IF(G466="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="467">
@@ -13598,17 +13598,17 @@
         <x:v>CALC02_Q4</x:v>
       </x:c>
       <x:c r="E468" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F468" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G468" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H468" s="14" t="n">
         <x:f>IF(G468="Yes",1,IF(G468="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="469">
@@ -13652,17 +13652,17 @@
         <x:v>CALC03_Q2</x:v>
       </x:c>
       <x:c r="E470" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F470" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G470" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H470" s="14" t="n">
         <x:f>IF(G470="Yes",1,IF(G470="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="471">
@@ -13679,17 +13679,17 @@
         <x:v>CALC03_Q3</x:v>
       </x:c>
       <x:c r="E471" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F471" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G471" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H471" s="14" t="n">
         <x:f>IF(G471="Yes",1,IF(G471="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="472">
@@ -13706,17 +13706,17 @@
         <x:v>CALC03_Q4</x:v>
       </x:c>
       <x:c r="E472" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F472" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G472" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H472" s="14" t="n">
         <x:f>IF(G472="Yes",1,IF(G472="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="473">
@@ -13787,17 +13787,17 @@
         <x:v>LIN01_Q3</x:v>
       </x:c>
       <x:c r="E475" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F475" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G475" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H475" s="14" t="n">
         <x:f>IF(G475="Yes",1,IF(G475="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="476">
@@ -13922,17 +13922,17 @@
         <x:v>LIN02_Q4</x:v>
       </x:c>
       <x:c r="E480" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F480" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G480" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H480" s="14" t="n">
         <x:f>IF(G480="Yes",1,IF(G480="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="481">
@@ -13949,17 +13949,17 @@
         <x:v>LIN03_Q1</x:v>
       </x:c>
       <x:c r="E481" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F481" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G481" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H481" s="14" t="n">
         <x:f>IF(G481="Yes",1,IF(G481="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="482">
@@ -14030,17 +14030,17 @@
         <x:v>LIN03_Q4</x:v>
       </x:c>
       <x:c r="E484" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F484" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G484" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H484" s="14" t="n">
         <x:f>IF(G484="Yes",1,IF(G484="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
@@ -14084,17 +14084,17 @@
         <x:v>ALG01_Q2</x:v>
       </x:c>
       <x:c r="E486" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F486" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G486" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H486" s="14" t="n">
         <x:f>IF(G486="Yes",1,IF(G486="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="487">
@@ -14111,17 +14111,17 @@
         <x:v>ALG01_Q3</x:v>
       </x:c>
       <x:c r="E487" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F487" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G487" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H487" s="14" t="n">
         <x:f>IF(G487="Yes",1,IF(G487="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="488">
@@ -14192,17 +14192,17 @@
         <x:v>ALG02_Q2</x:v>
       </x:c>
       <x:c r="E490" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F490" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G490" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H490" s="14" t="n">
         <x:f>IF(G490="Yes",1,IF(G490="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="491">
@@ -14246,17 +14246,17 @@
         <x:v>ALG02_Q4</x:v>
       </x:c>
       <x:c r="E492" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F492" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G492" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H492" s="14" t="n">
         <x:f>IF(G492="Yes",1,IF(G492="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
@@ -14300,17 +14300,17 @@
         <x:v>ALG03_Q2</x:v>
       </x:c>
       <x:c r="E494" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F494" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G494" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H494" s="14" t="n">
         <x:f>IF(G494="Yes",1,IF(G494="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="495">
@@ -14381,17 +14381,17 @@
         <x:v>ALG04_Q1</x:v>
       </x:c>
       <x:c r="E497" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F497" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G497" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H497" s="14" t="n">
         <x:f>IF(G497="Yes",1,IF(G497="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="498">
@@ -14408,17 +14408,17 @@
         <x:v>ALG04_Q2</x:v>
       </x:c>
       <x:c r="E498" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F498" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G498" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H498" s="14" t="n">
         <x:f>IF(G498="Yes",1,IF(G498="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="499">
@@ -14516,17 +14516,17 @@
         <x:v>CALC01_Q2</x:v>
       </x:c>
       <x:c r="E502" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F502" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G502" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H502" s="14" t="n">
         <x:f>IF(G502="Yes",1,IF(G502="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="503">
@@ -14543,17 +14543,17 @@
         <x:v>CALC01_Q3</x:v>
       </x:c>
       <x:c r="E503" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F503" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G503" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H503" s="14" t="n">
         <x:f>IF(G503="Yes",1,IF(G503="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="504">
@@ -14624,17 +14624,17 @@
         <x:v>CALC02_Q2</x:v>
       </x:c>
       <x:c r="E506" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F506" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G506" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H506" s="14" t="n">
         <x:f>IF(G506="Yes",1,IF(G506="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="507">
@@ -14678,17 +14678,17 @@
         <x:v>CALC02_Q4</x:v>
       </x:c>
       <x:c r="E508" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F508" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G508" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H508" s="14" t="n">
         <x:f>IF(G508="Yes",1,IF(G508="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="509">
@@ -14732,17 +14732,17 @@
         <x:v>CALC03_Q2</x:v>
       </x:c>
       <x:c r="E510" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F510" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G510" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H510" s="14" t="n">
         <x:f>IF(G510="Yes",1,IF(G510="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="511">
@@ -14813,17 +14813,17 @@
         <x:v>LIN01_Q1</x:v>
       </x:c>
       <x:c r="E513" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F513" s="13" t="str">
         <x:v>Functions</x:v>
       </x:c>
       <x:c r="G513" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H513" s="14" t="n">
         <x:f>IF(G513="Yes",1,IF(G513="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="514">
@@ -14840,17 +14840,17 @@
         <x:v>LIN01_Q2</x:v>
       </x:c>
       <x:c r="E514" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F514" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G514" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H514" s="14" t="n">
         <x:f>IF(G514="Yes",1,IF(G514="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="515">
@@ -14948,17 +14948,17 @@
         <x:v>LIN02_Q2</x:v>
       </x:c>
       <x:c r="E518" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F518" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G518" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H518" s="14" t="n">
         <x:f>IF(G518="Yes",1,IF(G518="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="519">
@@ -14975,17 +14975,17 @@
         <x:v>LIN02_Q3</x:v>
       </x:c>
       <x:c r="E519" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F519" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G519" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H519" s="14" t="n">
         <x:f>IF(G519="Yes",1,IF(G519="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="520">
@@ -15056,17 +15056,17 @@
         <x:v>LIN03_Q2</x:v>
       </x:c>
       <x:c r="E522" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F522" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G522" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H522" s="14" t="n">
         <x:f>IF(G522="Yes",1,IF(G522="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="523">
@@ -15110,17 +15110,17 @@
         <x:v>LIN03_Q4</x:v>
       </x:c>
       <x:c r="E524" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F524" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G524" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H524" s="14" t="n">
         <x:f>IF(G524="Yes",1,IF(G524="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="525">
@@ -15164,17 +15164,17 @@
         <x:v>ALG01_Q2</x:v>
       </x:c>
       <x:c r="E526" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F526" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G526" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H526" s="14" t="n">
         <x:f>IF(G526="Yes",1,IF(G526="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="527">
@@ -15299,17 +15299,17 @@
         <x:v>ALG02_Q3</x:v>
       </x:c>
       <x:c r="E531" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F531" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G531" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H531" s="14" t="n">
         <x:f>IF(G531="Yes",1,IF(G531="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="532">
@@ -15488,17 +15488,17 @@
         <x:v>ALG04_Q2</x:v>
       </x:c>
       <x:c r="E538" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F538" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G538" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H538" s="14" t="n">
         <x:f>IF(G538="Yes",1,IF(G538="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="539">
@@ -15596,17 +15596,17 @@
         <x:v>CALC01_Q2</x:v>
       </x:c>
       <x:c r="E542" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F542" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G542" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H542" s="14" t="n">
         <x:f>IF(G542="Yes",1,IF(G542="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="543">
@@ -15677,17 +15677,17 @@
         <x:v>CALC02_Q1</x:v>
       </x:c>
       <x:c r="E545" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F545" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G545" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H545" s="14" t="n">
         <x:f>IF(G545="Yes",1,IF(G545="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="546">
@@ -15731,17 +15731,17 @@
         <x:v>CALC02_Q3</x:v>
       </x:c>
       <x:c r="E547" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F547" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G547" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H547" s="14" t="n">
         <x:f>IF(G547="Yes",1,IF(G547="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="548">
@@ -15866,17 +15866,17 @@
         <x:v>CALC03_Q4</x:v>
       </x:c>
       <x:c r="E552" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F552" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G552" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H552" s="14" t="n">
         <x:f>IF(G552="Yes",1,IF(G552="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="553">
@@ -16028,17 +16028,17 @@
         <x:v>LIN02_Q2</x:v>
       </x:c>
       <x:c r="E558" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F558" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G558" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H558" s="14" t="n">
         <x:f>IF(G558="Yes",1,IF(G558="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="559">
@@ -16055,17 +16055,17 @@
         <x:v>LIN02_Q3</x:v>
       </x:c>
       <x:c r="E559" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F559" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G559" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H559" s="14" t="n">
         <x:f>IF(G559="Yes",1,IF(G559="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="560">
@@ -16163,17 +16163,17 @@
         <x:v>LIN03_Q3</x:v>
       </x:c>
       <x:c r="E563" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F563" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G563" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H563" s="14" t="n">
         <x:f>IF(G563="Yes",1,IF(G563="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="564">
@@ -16487,17 +16487,17 @@
         <x:v>ALG03_Q3</x:v>
       </x:c>
       <x:c r="E575" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F575" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G575" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H575" s="14" t="n">
         <x:f>IF(G575="Yes",1,IF(G575="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="576">
@@ -16541,17 +16541,17 @@
         <x:v>ALG04_Q1</x:v>
       </x:c>
       <x:c r="E577" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F577" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G577" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H577" s="14" t="n">
         <x:f>IF(G577="Yes",1,IF(G577="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="578">
@@ -16622,17 +16622,17 @@
         <x:v>ALG04_Q4</x:v>
       </x:c>
       <x:c r="E580" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F580" s="13" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G580" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H580" s="14" t="n">
         <x:f>IF(G580="Yes",1,IF(G580="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="581">
@@ -16730,17 +16730,17 @@
         <x:v>CALC01_Q4</x:v>
       </x:c>
       <x:c r="E584" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F584" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G584" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H584" s="14" t="n">
         <x:f>IF(G584="Yes",1,IF(G584="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="585">
@@ -17054,17 +17054,17 @@
         <x:v>LIN01_Q4</x:v>
       </x:c>
       <x:c r="E596" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F596" s="13" t="str">
         <x:v>6)</x:v>
       </x:c>
       <x:c r="G596" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H596" s="14" t="n">
         <x:f>IF(G596="Yes",1,IF(G596="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="597">
@@ -17108,17 +17108,17 @@
         <x:v>LIN02_Q2</x:v>
       </x:c>
       <x:c r="E598" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F598" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G598" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H598" s="14" t="n">
         <x:f>IF(G598="Yes",1,IF(G598="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="599">
@@ -17189,17 +17189,17 @@
         <x:v>LIN03_Q1</x:v>
       </x:c>
       <x:c r="E601" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F601" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G601" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H601" s="14" t="n">
         <x:f>IF(G601="Yes",1,IF(G601="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="602">
@@ -17297,17 +17297,17 @@
         <x:v>ALG01_Q1</x:v>
       </x:c>
       <x:c r="E605" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F605" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G605" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H605" s="14" t="n">
         <x:f>IF(G605="Yes",1,IF(G605="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="606">
@@ -17378,17 +17378,17 @@
         <x:v>ALG01_Q4</x:v>
       </x:c>
       <x:c r="E608" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F608" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G608" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H608" s="14" t="n">
         <x:f>IF(G608="Yes",1,IF(G608="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="609">
@@ -17432,17 +17432,17 @@
         <x:v>ALG02_Q2</x:v>
       </x:c>
       <x:c r="E610" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F610" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G610" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H610" s="14" t="n">
         <x:f>IF(G610="Yes",1,IF(G610="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="611">
@@ -17486,17 +17486,17 @@
         <x:v>ALG02_Q4</x:v>
       </x:c>
       <x:c r="E612" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F612" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G612" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H612" s="14" t="n">
         <x:f>IF(G612="Yes",1,IF(G612="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="613">
@@ -17567,17 +17567,17 @@
         <x:v>ALG03_Q3</x:v>
       </x:c>
       <x:c r="E615" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F615" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G615" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H615" s="14" t="n">
         <x:f>IF(G615="Yes",1,IF(G615="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="616">
@@ -17702,17 +17702,17 @@
         <x:v>ALG04_Q4</x:v>
       </x:c>
       <x:c r="E620" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F620" s="13" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G620" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H620" s="14" t="n">
         <x:f>IF(G620="Yes",1,IF(G620="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="621">
@@ -17729,17 +17729,17 @@
         <x:v>CALC01_Q1</x:v>
       </x:c>
       <x:c r="E621" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F621" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G621" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H621" s="14" t="n">
         <x:f>IF(G621="Yes",1,IF(G621="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="622">
@@ -17810,17 +17810,17 @@
         <x:v>CALC01_Q4</x:v>
       </x:c>
       <x:c r="E624" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F624" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G624" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H624" s="14" t="n">
         <x:f>IF(G624="Yes",1,IF(G624="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="625">
@@ -17864,17 +17864,17 @@
         <x:v>CALC02_Q2</x:v>
       </x:c>
       <x:c r="E626" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F626" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G626" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H626" s="14" t="n">
         <x:f>IF(G626="Yes",1,IF(G626="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="627">
@@ -17918,17 +17918,17 @@
         <x:v>CALC02_Q4</x:v>
       </x:c>
       <x:c r="E628" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F628" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G628" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H628" s="14" t="n">
         <x:f>IF(G628="Yes",1,IF(G628="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="629">
@@ -17999,17 +17999,17 @@
         <x:v>CALC03_Q3</x:v>
       </x:c>
       <x:c r="E631" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F631" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G631" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H631" s="14" t="n">
         <x:f>IF(G631="Yes",1,IF(G631="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="632">
@@ -18134,17 +18134,17 @@
         <x:v>LIN01_Q4</x:v>
       </x:c>
       <x:c r="E636" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F636" s="13" t="str">
         <x:v>6)</x:v>
       </x:c>
       <x:c r="G636" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H636" s="14" t="n">
         <x:f>IF(G636="Yes",1,IF(G636="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="637">
@@ -18161,17 +18161,17 @@
         <x:v>LIN02_Q1</x:v>
       </x:c>
       <x:c r="E637" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F637" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G637" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H637" s="14" t="n">
         <x:f>IF(G637="Yes",1,IF(G637="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="638">
@@ -18242,17 +18242,17 @@
         <x:v>LIN02_Q4</x:v>
       </x:c>
       <x:c r="E640" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F640" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G640" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H640" s="14" t="n">
         <x:f>IF(G640="Yes",1,IF(G640="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="641">
@@ -18296,17 +18296,17 @@
         <x:v>LIN03_Q2</x:v>
       </x:c>
       <x:c r="E642" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F642" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G642" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H642" s="14" t="n">
         <x:f>IF(G642="Yes",1,IF(G642="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="643">
@@ -18350,17 +18350,17 @@
         <x:v>LIN03_Q4</x:v>
       </x:c>
       <x:c r="E644" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F644" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G644" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H644" s="14" t="n">
         <x:f>IF(G644="Yes",1,IF(G644="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="645">
@@ -18404,17 +18404,17 @@
         <x:v>ALG01_Q2</x:v>
       </x:c>
       <x:c r="E646" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F646" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G646" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H646" s="14" t="n">
         <x:f>IF(G646="Yes",1,IF(G646="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="647">
@@ -18458,17 +18458,17 @@
         <x:v>ALG01_Q4</x:v>
       </x:c>
       <x:c r="E648" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F648" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G648" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H648" s="14" t="n">
         <x:f>IF(G648="Yes",1,IF(G648="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="649">
@@ -18485,17 +18485,17 @@
         <x:v>ALG02_Q1</x:v>
       </x:c>
       <x:c r="E649" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F649" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G649" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H649" s="14" t="n">
         <x:f>IF(G649="Yes",1,IF(G649="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="650">
@@ -18512,17 +18512,17 @@
         <x:v>ALG02_Q2</x:v>
       </x:c>
       <x:c r="E650" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F650" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G650" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H650" s="14" t="n">
         <x:f>IF(G650="Yes",1,IF(G650="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="651">
@@ -18728,17 +18728,17 @@
         <x:v>ALG04_Q2</x:v>
       </x:c>
       <x:c r="E658" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F658" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G658" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H658" s="14" t="n">
         <x:f>IF(G658="Yes",1,IF(G658="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="659">
@@ -18755,17 +18755,17 @@
         <x:v>ALG04_Q3</x:v>
       </x:c>
       <x:c r="E659" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F659" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G659" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H659" s="14" t="n">
         <x:f>IF(G659="Yes",1,IF(G659="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="660">
@@ -18782,17 +18782,17 @@
         <x:v>ALG04_Q4</x:v>
       </x:c>
       <x:c r="E660" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F660" s="13" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G660" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H660" s="14" t="n">
         <x:f>IF(G660="Yes",1,IF(G660="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="661">
@@ -18836,17 +18836,17 @@
         <x:v>CALC01_Q2</x:v>
       </x:c>
       <x:c r="E662" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F662" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G662" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H662" s="14" t="n">
         <x:f>IF(G662="Yes",1,IF(G662="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="663">
@@ -18890,17 +18890,17 @@
         <x:v>CALC01_Q4</x:v>
       </x:c>
       <x:c r="E664" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F664" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G664" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H664" s="14" t="n">
         <x:f>IF(G664="Yes",1,IF(G664="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="665">
@@ -18917,17 +18917,17 @@
         <x:v>CALC02_Q1</x:v>
       </x:c>
       <x:c r="E665" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F665" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G665" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H665" s="14" t="n">
         <x:f>IF(G665="Yes",1,IF(G665="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="666">
@@ -18944,17 +18944,17 @@
         <x:v>CALC02_Q2</x:v>
       </x:c>
       <x:c r="E666" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F666" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G666" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H666" s="14" t="n">
         <x:f>IF(G666="Yes",1,IF(G666="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="667">
@@ -19025,17 +19025,17 @@
         <x:v>CALC03_Q1</x:v>
       </x:c>
       <x:c r="E669" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F669" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G669" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H669" s="14" t="n">
         <x:f>IF(G669="Yes",1,IF(G669="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="670">
@@ -19160,17 +19160,17 @@
         <x:v>LIN01_Q2</x:v>
       </x:c>
       <x:c r="E674" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F674" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G674" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H674" s="14" t="n">
         <x:f>IF(G674="Yes",1,IF(G674="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="675">
@@ -19187,17 +19187,17 @@
         <x:v>LIN01_Q3</x:v>
       </x:c>
       <x:c r="E675" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F675" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G675" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H675" s="14" t="n">
         <x:f>IF(G675="Yes",1,IF(G675="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="676">
@@ -19268,17 +19268,17 @@
         <x:v>LIN02_Q2</x:v>
       </x:c>
       <x:c r="E678" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F678" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G678" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H678" s="14" t="n">
         <x:f>IF(G678="Yes",1,IF(G678="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="679">
@@ -19322,17 +19322,17 @@
         <x:v>LIN02_Q4</x:v>
       </x:c>
       <x:c r="E680" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F680" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G680" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H680" s="14" t="n">
         <x:f>IF(G680="Yes",1,IF(G680="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="681">
@@ -19349,17 +19349,17 @@
         <x:v>LIN03_Q1</x:v>
       </x:c>
       <x:c r="E681" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F681" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G681" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H681" s="14" t="n">
         <x:f>IF(G681="Yes",1,IF(G681="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="682">
@@ -19376,17 +19376,17 @@
         <x:v>LIN03_Q2</x:v>
       </x:c>
       <x:c r="E682" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F682" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G682" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H682" s="14" t="n">
         <x:f>IF(G682="Yes",1,IF(G682="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="683">
@@ -19538,17 +19538,17 @@
         <x:v>ALG01_Q4</x:v>
       </x:c>
       <x:c r="E688" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F688" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G688" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H688" s="14" t="n">
         <x:f>IF(G688="Yes",1,IF(G688="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="689">
@@ -19565,17 +19565,17 @@
         <x:v>ALG02_Q1</x:v>
       </x:c>
       <x:c r="E689" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F689" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G689" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H689" s="14" t="n">
         <x:f>IF(G689="Yes",1,IF(G689="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="690">
@@ -19673,17 +19673,17 @@
         <x:v>ALG03_Q1</x:v>
       </x:c>
       <x:c r="E693" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F693" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G693" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H693" s="14" t="n">
         <x:f>IF(G693="Yes",1,IF(G693="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="694">
@@ -19754,17 +19754,17 @@
         <x:v>ALG03_Q4</x:v>
       </x:c>
       <x:c r="E696" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F696" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G696" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H696" s="14" t="n">
         <x:f>IF(G696="Yes",1,IF(G696="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="697">
@@ -19808,17 +19808,17 @@
         <x:v>ALG04_Q2</x:v>
       </x:c>
       <x:c r="E698" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F698" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G698" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H698" s="14" t="n">
         <x:f>IF(G698="Yes",1,IF(G698="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="699">
@@ -19943,17 +19943,17 @@
         <x:v>CALC01_Q3</x:v>
       </x:c>
       <x:c r="E703" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F703" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G703" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H703" s="14" t="n">
         <x:f>IF(G703="Yes",1,IF(G703="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="704">
@@ -19970,17 +19970,17 @@
         <x:v>CALC01_Q4</x:v>
       </x:c>
       <x:c r="E704" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F704" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G704" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H704" s="14" t="n">
         <x:f>IF(G704="Yes",1,IF(G704="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="705">
@@ -20105,17 +20105,17 @@
         <x:v>CALC03_Q1</x:v>
       </x:c>
       <x:c r="E709" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F709" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G709" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H709" s="14" t="n">
         <x:f>IF(G709="Yes",1,IF(G709="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="710">
@@ -20132,17 +20132,17 @@
         <x:v>CALC03_Q2</x:v>
       </x:c>
       <x:c r="E710" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F710" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G710" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H710" s="14" t="n">
         <x:f>IF(G710="Yes",1,IF(G710="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="711">
@@ -20240,17 +20240,17 @@
         <x:v>LIN01_Q2</x:v>
       </x:c>
       <x:c r="E714" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F714" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G714" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H714" s="14" t="n">
         <x:f>IF(G714="Yes",1,IF(G714="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="715">
@@ -20321,17 +20321,17 @@
         <x:v>LIN02_Q1</x:v>
       </x:c>
       <x:c r="E717" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F717" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G717" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H717" s="14" t="n">
         <x:f>IF(G717="Yes",1,IF(G717="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="718">
@@ -20402,17 +20402,17 @@
         <x:v>LIN02_Q4</x:v>
       </x:c>
       <x:c r="E720" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F720" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G720" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H720" s="14" t="n">
         <x:f>IF(G720="Yes",1,IF(G720="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="721">
@@ -20510,17 +20510,17 @@
         <x:v>LIN03_Q4</x:v>
       </x:c>
       <x:c r="E724" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F724" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G724" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H724" s="14" t="n">
         <x:f>IF(G724="Yes",1,IF(G724="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="725">
@@ -20618,17 +20618,17 @@
         <x:v>ALG01_Q4</x:v>
       </x:c>
       <x:c r="E728" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F728" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G728" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H728" s="14" t="n">
         <x:f>IF(G728="Yes",1,IF(G728="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="729">
@@ -20699,17 +20699,17 @@
         <x:v>ALG02_Q3</x:v>
       </x:c>
       <x:c r="E731" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F731" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G731" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H731" s="14" t="n">
         <x:f>IF(G731="Yes",1,IF(G731="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="732">
@@ -20807,17 +20807,17 @@
         <x:v>ALG03_Q3</x:v>
       </x:c>
       <x:c r="E735" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F735" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G735" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H735" s="14" t="n">
         <x:f>IF(G735="Yes",1,IF(G735="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="736">
@@ -20834,17 +20834,17 @@
         <x:v>ALG03_Q4</x:v>
       </x:c>
       <x:c r="E736" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F736" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G736" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H736" s="14" t="n">
         <x:f>IF(G736="Yes",1,IF(G736="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="737">
@@ -20996,17 +20996,17 @@
         <x:v>CALC01_Q2</x:v>
       </x:c>
       <x:c r="E742" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F742" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G742" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H742" s="14" t="n">
         <x:f>IF(G742="Yes",1,IF(G742="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="743">
@@ -21131,17 +21131,17 @@
         <x:v>CALC02_Q3</x:v>
       </x:c>
       <x:c r="E747" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F747" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G747" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H747" s="14" t="n">
         <x:f>IF(G747="Yes",1,IF(G747="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="748">
@@ -21185,17 +21185,17 @@
         <x:v>CALC03_Q1</x:v>
       </x:c>
       <x:c r="E749" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F749" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G749" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H749" s="14" t="n">
         <x:f>IF(G749="Yes",1,IF(G749="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="750">
@@ -21266,17 +21266,17 @@
         <x:v>CALC03_Q4</x:v>
       </x:c>
       <x:c r="E752" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F752" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G752" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H752" s="14" t="n">
         <x:f>IF(G752="Yes",1,IF(G752="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="753">
@@ -21374,17 +21374,17 @@
         <x:v>LIN01_Q4</x:v>
       </x:c>
       <x:c r="E756" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F756" s="13" t="str">
         <x:v>6)</x:v>
       </x:c>
       <x:c r="G756" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H756" s="14" t="n">
         <x:f>IF(G756="Yes",1,IF(G756="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="757">
@@ -21563,17 +21563,17 @@
         <x:v>LIN03_Q3</x:v>
       </x:c>
       <x:c r="E763" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F763" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G763" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H763" s="14" t="n">
         <x:f>IF(G763="Yes",1,IF(G763="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="764">
@@ -21644,17 +21644,17 @@
         <x:v>ALG01_Q2</x:v>
       </x:c>
       <x:c r="E766" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F766" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G766" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H766" s="14" t="n">
         <x:f>IF(G766="Yes",1,IF(G766="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="767">
@@ -21698,17 +21698,17 @@
         <x:v>ALG01_Q4</x:v>
       </x:c>
       <x:c r="E768" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F768" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G768" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H768" s="14" t="n">
         <x:f>IF(G768="Yes",1,IF(G768="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="769">
@@ -21914,17 +21914,17 @@
         <x:v>ALG03_Q4</x:v>
       </x:c>
       <x:c r="E776" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F776" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G776" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H776" s="14" t="n">
         <x:f>IF(G776="Yes",1,IF(G776="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="777">
@@ -21941,17 +21941,17 @@
         <x:v>ALG04_Q1</x:v>
       </x:c>
       <x:c r="E777" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F777" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G777" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H777" s="14" t="n">
         <x:f>IF(G777="Yes",1,IF(G777="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="778">
@@ -22022,17 +22022,17 @@
         <x:v>ALG04_Q4</x:v>
       </x:c>
       <x:c r="E780" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F780" s="13" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="G780" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H780" s="14" t="n">
         <x:f>IF(G780="Yes",1,IF(G780="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="781">
@@ -22076,17 +22076,17 @@
         <x:v>CALC01_Q2</x:v>
       </x:c>
       <x:c r="E782" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F782" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G782" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H782" s="14" t="n">
         <x:f>IF(G782="Yes",1,IF(G782="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="783">
@@ -22130,17 +22130,17 @@
         <x:v>CALC01_Q4</x:v>
       </x:c>
       <x:c r="E784" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F784" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G784" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H784" s="14" t="n">
         <x:f>IF(G784="Yes",1,IF(G784="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="785">
@@ -22346,17 +22346,17 @@
         <x:v>CALC03_Q4</x:v>
       </x:c>
       <x:c r="E792" s="13" t="str">
-        <x:v>D</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F792" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G792" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H792" s="14" t="n">
         <x:f>IF(G792="Yes",1,IF(G792="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="793">
@@ -22373,17 +22373,17 @@
         <x:v>LIN01_Q1</x:v>
       </x:c>
       <x:c r="E793" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F793" s="13" t="str">
         <x:v>Functions</x:v>
       </x:c>
       <x:c r="G793" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H793" s="14" t="n">
         <x:f>IF(G793="Yes",1,IF(G793="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="794">
@@ -22454,17 +22454,17 @@
         <x:v>LIN01_Q4</x:v>
       </x:c>
       <x:c r="E796" s="13" t="str">
-        <x:v>B</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F796" s="13" t="str">
         <x:v>6)</x:v>
       </x:c>
       <x:c r="G796" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H796" s="14" t="n">
         <x:f>IF(G796="Yes",1,IF(G796="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="797">
@@ -22508,17 +22508,17 @@
         <x:v>LIN02_Q2</x:v>
       </x:c>
       <x:c r="E798" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="F798" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G798" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H798" s="14" t="n">
         <x:f>IF(G798="Yes",1,IF(G798="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="799">
@@ -22562,17 +22562,17 @@
         <x:v>LIN02_Q4</x:v>
       </x:c>
       <x:c r="E800" s="13" t="str">
-        <x:v>C</x:v>
+        <x:v>A</x:v>
       </x:c>
       <x:c r="F800" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G800" s="13" t="str">
-        <x:v>No</x:v>
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="H800" s="14" t="n">
         <x:f>IF(G800="Yes",1,IF(G800="No",0,""))</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="801">
@@ -22643,17 +22643,17 @@
         <x:v>LIN03_Q3</x:v>
       </x:c>
       <x:c r="E803" s="13" t="str">
-        <x:v>A</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F803" s="13" t="str">
         <x:v>A</x:v>
       </x:c>
       <x:c r="G803" s="13" t="str">
-        <x:v>Yes</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H803" s="14" t="n">
         <x:f>IF(G803="Yes",1,IF(G803="No",0,""))</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="804">

--- a/study/analysis/mathontospeak_synthetic_demo_analysis.xlsx
+++ b/study/analysis/mathontospeak_synthetic_demo_analysis.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R26c565d4f3324d80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stimuli" sheetId="2" r:id="Rdc4dd7dbfad04717"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counterbalance" sheetId="3" r:id="Re9e75771b1984074"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comprehension Scores" sheetId="4" r:id="R81de29042b6846c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NASA TLX" sheetId="5" r:id="Refa57c2005604abc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCQ Items" sheetId="6" r:id="R5300ce425b8a4a81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Coding" sheetId="7" r:id="R0a3abe2d5a2c4fe3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo Provenance" sheetId="8" r:id="R566f88930fea424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9f7f107121f5467d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stimuli" sheetId="2" r:id="R4d42044e22fc4797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counterbalance" sheetId="3" r:id="R30f2f47b14614328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comprehension Scores" sheetId="4" r:id="R86b2818476194f5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NASA TLX" sheetId="5" r:id="Rafa73158617c4724"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MCQ Items" sheetId="6" r:id="Raf00b1faf92745b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interview Coding" sheetId="7" r:id="R7d18ff6ff6e04710"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demo Provenance" sheetId="8" r:id="R851dc114ebfb4a68"/>
   </x:sheets>
 </x:workbook>
 </file>
